--- a/daily/2026-04-03.xlsx
+++ b/daily/2026-04-03.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X104"/>
+  <dimension ref="A1:X106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="n">
         <v>22</v>
@@ -688,13 +688,13 @@
         <v>7.9</v>
       </c>
       <c r="O3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
         <v>0.3</v>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="E4" t="n">
         <v>16</v>
@@ -770,13 +770,13 @@
         <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R4" t="n">
         <v>-2.1</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E7" t="n">
         <v>12.7</v>
@@ -1022,7 +1022,7 @@
         <v>45</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="E8" t="n">
         <v>18.3</v>
@@ -1101,10 +1101,10 @@
         <v>50</v>
       </c>
       <c r="P8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="R8" t="n">
         <v>0.7</v>
@@ -1461,7 +1461,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1475,71 +1475,75 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>15.3</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>15.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>18.7</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>16.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>16.8</v>
       </c>
       <c r="J13" t="n">
-        <v>19.1</v>
+        <v>20.9</v>
       </c>
       <c r="K13" t="n">
-        <v>16.2</v>
+        <v>24.5</v>
       </c>
       <c r="L13" t="n">
-        <v>33.3</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>39</v>
+        <v>43.4</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
-        <v>22</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>19.4 (7g)</t>
+        </is>
+      </c>
       <c r="X13" t="n">
-        <v>6.5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1553,69 +1557,65 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="E14" t="n">
-        <v>15.3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>15.8</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>18.7</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
-        <v>16.1</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>16.8</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
-        <v>20.9</v>
+        <v>19.1</v>
       </c>
       <c r="K14" t="n">
-        <v>24.5</v>
+        <v>16.2</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>33.3</v>
       </c>
       <c r="M14" t="n">
-        <v>43.4</v>
+        <v>39</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P14" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3</v>
+        <v>-3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="S14" t="n">
-        <v>5.6</v>
+        <v>-5.7</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
+        <v>9</v>
+      </c>
+      <c r="V14" t="n">
         <v>22</v>
       </c>
-      <c r="V14" t="n">
-        <v>13</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>19.4 (7g)</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>-4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="E15" t="n">
         <v>28</v>
@@ -1668,13 +1668,13 @@
         <v>9.9</v>
       </c>
       <c r="O15" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.7</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
         <v>7.6</v>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
@@ -1752,7 +1752,7 @@
         <v>45</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.7</v>
+        <v>-0.7</v>
       </c>
       <c r="R16" t="n">
         <v>2.6</v>
@@ -1859,7 +1859,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Adem Bona</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1869,79 +1869,75 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>26.5</v>
       </c>
       <c r="E18" t="n">
-        <v>5.7</v>
+        <v>25.7</v>
       </c>
       <c r="F18" t="n">
-        <v>4.8</v>
+        <v>26.6</v>
       </c>
       <c r="G18" t="n">
-        <v>6.5</v>
+        <v>28.6</v>
       </c>
       <c r="H18" t="n">
-        <v>6.3</v>
+        <v>27.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>26.7</v>
       </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>37.2</v>
       </c>
       <c r="K18" t="n">
-        <v>18.5</v>
+        <v>37</v>
       </c>
       <c r="L18" t="n">
-        <v>55.2</v>
+        <v>45.6</v>
       </c>
       <c r="M18" t="n">
-        <v>59.1</v>
+        <v>44.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P18" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.9</v>
+        <v>1.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="U18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>4.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>-1.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1951,69 +1947,69 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>28.5</v>
       </c>
       <c r="E19" t="n">
-        <v>25.7</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>26.6</v>
+        <v>28.6</v>
       </c>
       <c r="G19" t="n">
-        <v>28.6</v>
+        <v>31.2</v>
       </c>
       <c r="H19" t="n">
-        <v>27.9</v>
+        <v>30.1</v>
       </c>
       <c r="I19" t="n">
-        <v>26.7</v>
+        <v>28.3</v>
       </c>
       <c r="J19" t="n">
-        <v>37.2</v>
+        <v>33.4</v>
       </c>
       <c r="K19" t="n">
-        <v>37</v>
+        <v>32.8</v>
       </c>
       <c r="L19" t="n">
-        <v>45.6</v>
+        <v>52.5</v>
       </c>
       <c r="M19" t="n">
-        <v>44.5</v>
+        <v>50.7</v>
       </c>
       <c r="N19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V19" t="n">
         <v>16</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2033,7 +2029,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E20" t="n">
         <v>4.3</v>
@@ -2066,13 +2062,13 @@
         <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P20" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
         <v>-3.3</v>
@@ -2111,7 +2107,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="E21" t="n">
         <v>10.7</v>
@@ -2144,13 +2140,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P21" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="R21" t="n">
         <v>-0.8</v>
@@ -2349,7 +2345,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="E24" t="n">
         <v>10.3</v>
@@ -2382,13 +2378,13 @@
         <v>8.6</v>
       </c>
       <c r="O24" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="P24" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1</v>
+        <v>5.1</v>
       </c>
       <c r="R24" t="n">
         <v>0.2</v>
@@ -2431,7 +2427,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="E25" t="n">
         <v>26</v>
@@ -2470,7 +2466,7 @@
         <v>65</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R25" t="n">
         <v>-3.5</v>
@@ -2595,7 +2591,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="E27" t="n">
         <v>16.3</v>
@@ -2631,10 +2627,10 @@
         <v>70</v>
       </c>
       <c r="P27" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
         <v>4.4</v>
@@ -2997,7 +2993,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="E32" t="n">
         <v>8</v>
@@ -3030,13 +3026,13 @@
         <v>5.2</v>
       </c>
       <c r="O32" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P32" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="R32" t="n">
         <v>-4.9</v>
@@ -3395,7 +3391,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E37" t="n">
         <v>13</v>
@@ -3428,13 +3424,13 @@
         <v>7.2</v>
       </c>
       <c r="O37" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P37" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
       <c r="R37" t="n">
         <v>1.3</v>
@@ -3641,7 +3637,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E40" t="n">
         <v>4</v>
@@ -3674,13 +3670,13 @@
         <v>3.4</v>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P40" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="R40" t="n">
         <v>0.4</v>
@@ -3719,7 +3715,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="E41" t="n">
         <v>9</v>
@@ -3752,13 +3748,13 @@
         <v>4.9</v>
       </c>
       <c r="O41" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P41" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R41" t="n">
         <v>2</v>
@@ -3801,7 +3797,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="n">
         <v>11</v>
@@ -3834,13 +3830,13 @@
         <v>7.8</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P42" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="R42" t="n">
         <v>-0.5</v>
@@ -4539,7 +4535,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="n">
         <v>18</v>
@@ -4572,13 +4568,13 @@
         <v>9.6</v>
       </c>
       <c r="O51" t="n">
+        <v>40</v>
+      </c>
+      <c r="P51" t="n">
         <v>30</v>
       </c>
-      <c r="P51" t="n">
-        <v>20</v>
-      </c>
       <c r="Q51" t="n">
-        <v>-4.4</v>
+        <v>-3.4</v>
       </c>
       <c r="R51" t="n">
         <v>7.3</v>
@@ -4781,7 +4777,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E54" t="n">
         <v>16.3</v>
@@ -4814,13 +4810,13 @@
         <v>11</v>
       </c>
       <c r="O54" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P54" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Q54" t="n">
-        <v>-4.4</v>
+        <v>-3.4</v>
       </c>
       <c r="R54" t="n">
         <v>6.3</v>
@@ -4863,7 +4859,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E55" t="n">
         <v>10.7</v>
@@ -4902,7 +4898,7 @@
         <v>35</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="R55" t="n">
         <v>-3</v>
@@ -5355,7 +5351,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="E61" t="n">
         <v>16.3</v>
@@ -5388,13 +5384,13 @@
         <v>4.8</v>
       </c>
       <c r="O61" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P61" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="R61" t="n">
         <v>-1.8</v>
@@ -5437,7 +5433,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E62" t="n">
         <v>23.7</v>
@@ -5470,13 +5466,13 @@
         <v>7.5</v>
       </c>
       <c r="O62" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q62" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="R62" t="n">
         <v>6.3</v>
@@ -5765,7 +5761,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="E66" t="n">
         <v>24.7</v>
@@ -5804,7 +5800,7 @@
         <v>40</v>
       </c>
       <c r="Q66" t="n">
-        <v>-1</v>
+        <v>-0</v>
       </c>
       <c r="R66" t="n">
         <v>4.1</v>
@@ -6175,7 +6171,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="E71" t="n">
         <v>17.7</v>
@@ -6214,7 +6210,7 @@
         <v>40</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="R71" t="n">
         <v>-5.3</v>
@@ -6565,7 +6561,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E76" t="n">
         <v>11.3</v>
@@ -6598,13 +6594,13 @@
         <v>5.1</v>
       </c>
       <c r="O76" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P76" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q76" t="n">
-        <v>-2.9</v>
+        <v>-1.9</v>
       </c>
       <c r="R76" t="n">
         <v>2.8</v>
@@ -6725,7 +6721,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E78" t="n">
         <v>15.3</v>
@@ -6761,10 +6757,10 @@
         <v>50</v>
       </c>
       <c r="P78" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q78" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="R78" t="n">
         <v>0.4</v>
@@ -6949,7 +6945,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6959,75 +6955,75 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E81" t="n">
-        <v>10.3</v>
+        <v>14.3</v>
       </c>
       <c r="F81" t="n">
-        <v>12.6</v>
+        <v>10.8</v>
       </c>
       <c r="G81" t="n">
-        <v>17.3</v>
+        <v>11.9</v>
       </c>
       <c r="H81" t="n">
-        <v>20.2</v>
+        <v>13.2</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>14.4</v>
       </c>
       <c r="J81" t="n">
-        <v>25.6</v>
+        <v>20.8</v>
       </c>
       <c r="K81" t="n">
-        <v>31.2</v>
+        <v>22.1</v>
       </c>
       <c r="L81" t="n">
-        <v>47.4</v>
+        <v>44.7</v>
       </c>
       <c r="M81" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="N81" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="O81" t="n">
+        <v>30</v>
+      </c>
+      <c r="P81" t="n">
         <v>50</v>
       </c>
-      <c r="P81" t="n">
-        <v>75</v>
-      </c>
       <c r="Q81" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="R81" t="n">
-        <v>-8.4</v>
+        <v>-3.6</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.6</v>
+        <v>-6.1</v>
       </c>
       <c r="T81" t="n">
-        <v>-5.6</v>
+        <v>-1.4</v>
       </c>
       <c r="U81" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V81" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
-        <v>-13.1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7037,75 +7033,79 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E82" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
-        <v>10.8</v>
+        <v>11.6</v>
       </c>
       <c r="G82" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="H82" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="I82" t="n">
-        <v>14.4</v>
+        <v>11.2</v>
       </c>
       <c r="J82" t="n">
-        <v>20.8</v>
+        <v>29.3</v>
       </c>
       <c r="K82" t="n">
-        <v>22.1</v>
+        <v>28.8</v>
       </c>
       <c r="L82" t="n">
-        <v>44.7</v>
+        <v>55</v>
       </c>
       <c r="M82" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="N82" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="O82" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P82" t="n">
         <v>60</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.9</v>
+        <v>-0.3</v>
       </c>
       <c r="R82" t="n">
-        <v>-3.6</v>
+        <v>0.4</v>
       </c>
       <c r="S82" t="n">
-        <v>-6.1</v>
+        <v>3.4</v>
       </c>
       <c r="T82" t="n">
-        <v>-1.4</v>
+        <v>0.5</v>
       </c>
       <c r="U82" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="V82" t="n">
-        <v>29</v>
-      </c>
-      <c r="W82" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>11.0 (3g)</t>
+        </is>
+      </c>
       <c r="X82" t="n">
-        <v>-1.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7119,55 +7119,55 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E83" t="n">
-        <v>9.300000000000001</v>
+        <v>16</v>
       </c>
       <c r="F83" t="n">
-        <v>7.6</v>
+        <v>15.8</v>
       </c>
       <c r="G83" t="n">
-        <v>9.5</v>
+        <v>15.8</v>
       </c>
       <c r="H83" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I83" t="n">
         <v>10.7</v>
       </c>
-      <c r="I83" t="n">
-        <v>11.5</v>
-      </c>
       <c r="J83" t="n">
-        <v>19.2</v>
+        <v>23.6</v>
       </c>
       <c r="K83" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="L83" t="n">
-        <v>35.4</v>
+        <v>73</v>
       </c>
       <c r="M83" t="n">
-        <v>40.2</v>
+        <v>62.7</v>
       </c>
       <c r="N83" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="O83" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="P83" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q83" t="n">
-        <v>2</v>
+        <v>-0.8</v>
       </c>
       <c r="R83" t="n">
-        <v>-3.9</v>
+        <v>5.1</v>
       </c>
       <c r="S83" t="n">
-        <v>-4.8</v>
+        <v>10.3</v>
       </c>
       <c r="T83" t="n">
-        <v>-3.8</v>
+        <v>1.2</v>
       </c>
       <c r="U83" t="n">
         <v>8</v>
@@ -7175,19 +7175,15 @@
       <c r="V83" t="n">
         <v>29</v>
       </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>10.0 (7g)</t>
-        </is>
-      </c>
+      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
-        <v>-3.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7197,79 +7193,79 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="F84" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="G84" t="n">
-        <v>18.2</v>
+        <v>17.9</v>
       </c>
       <c r="H84" t="n">
-        <v>17.6</v>
+        <v>20.6</v>
       </c>
       <c r="I84" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="J84" t="n">
-        <v>30.8</v>
+        <v>32.7</v>
       </c>
       <c r="K84" t="n">
-        <v>30.7</v>
+        <v>34.1</v>
       </c>
       <c r="L84" t="n">
-        <v>46.5</v>
+        <v>44.6</v>
       </c>
       <c r="M84" t="n">
-        <v>48.3</v>
+        <v>52.6</v>
       </c>
       <c r="N84" t="n">
-        <v>9.1</v>
+        <v>3.8</v>
       </c>
       <c r="O84" t="n">
+        <v>30</v>
+      </c>
+      <c r="P84" t="n">
         <v>50</v>
       </c>
-      <c r="P84" t="n">
-        <v>45</v>
-      </c>
       <c r="Q84" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="S84" t="n">
-        <v>-1.8</v>
+        <v>-8</v>
       </c>
       <c r="T84" t="n">
-        <v>0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="U84" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V84" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>5.3 (3g)</t>
+          <t>20.0 (3g)</t>
         </is>
       </c>
       <c r="X84" t="n">
-        <v>-19.7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7283,71 +7279,75 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="E85" t="n">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
       <c r="F85" t="n">
-        <v>12.4</v>
+        <v>9.4</v>
       </c>
       <c r="G85" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="H85" t="n">
-        <v>12.8</v>
+        <v>11.4</v>
       </c>
       <c r="I85" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="J85" t="n">
-        <v>30.9</v>
+        <v>21.1</v>
       </c>
       <c r="K85" t="n">
-        <v>28.3</v>
+        <v>21.5</v>
       </c>
       <c r="L85" t="n">
-        <v>42.4</v>
+        <v>40</v>
       </c>
       <c r="M85" t="n">
-        <v>42.2</v>
+        <v>40.4</v>
       </c>
       <c r="N85" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="O85" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P85" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2</v>
+        <v>2.6</v>
       </c>
       <c r="R85" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="S85" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="T85" t="n">
-        <v>2.5</v>
+        <v>-0.4</v>
       </c>
       <c r="U85" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="V85" t="n">
-        <v>2</v>
-      </c>
-      <c r="W85" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>15.0 (3g)</t>
+        </is>
+      </c>
       <c r="X85" t="n">
-        <v>-7.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7357,79 +7357,75 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="E86" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="F86" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="G86" t="n">
-        <v>13.1</v>
+        <v>17.3</v>
       </c>
       <c r="H86" t="n">
-        <v>12.8</v>
+        <v>20.2</v>
       </c>
       <c r="I86" t="n">
-        <v>11.2</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>29.3</v>
+        <v>25.6</v>
       </c>
       <c r="K86" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="L86" t="n">
-        <v>55</v>
+        <v>47.4</v>
       </c>
       <c r="M86" t="n">
-        <v>51.7</v>
+        <v>48</v>
       </c>
       <c r="N86" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O86" t="n">
+        <v>50</v>
+      </c>
+      <c r="P86" t="n">
         <v>70</v>
       </c>
-      <c r="P86" t="n">
-        <v>60</v>
-      </c>
       <c r="Q86" t="n">
-        <v>-0.3</v>
+        <v>5.5</v>
       </c>
       <c r="R86" t="n">
-        <v>0.4</v>
+        <v>-8.4</v>
       </c>
       <c r="S86" t="n">
-        <v>3.4</v>
+        <v>-0.6</v>
       </c>
       <c r="T86" t="n">
-        <v>0.5</v>
+        <v>-5.6</v>
       </c>
       <c r="U86" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="V86" t="n">
         <v>2</v>
       </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>11.0 (3g)</t>
-        </is>
-      </c>
+      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
-        <v>10</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7443,55 +7439,55 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
       <c r="E87" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="F87" t="n">
-        <v>22.6</v>
+        <v>17.8</v>
       </c>
       <c r="G87" t="n">
-        <v>22.1</v>
+        <v>18.2</v>
       </c>
       <c r="H87" t="n">
-        <v>22.1</v>
+        <v>17.6</v>
       </c>
       <c r="I87" t="n">
-        <v>21.5</v>
+        <v>17.8</v>
       </c>
       <c r="J87" t="n">
-        <v>34.4</v>
+        <v>30.8</v>
       </c>
       <c r="K87" t="n">
-        <v>32.9</v>
+        <v>30.7</v>
       </c>
       <c r="L87" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="M87" t="n">
-        <v>44.4</v>
+        <v>48.3</v>
       </c>
       <c r="N87" t="n">
-        <v>5.8</v>
+        <v>9.1</v>
       </c>
       <c r="O87" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P87" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q87" t="n">
-        <v>-2</v>
+        <v>1.3</v>
       </c>
       <c r="R87" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="T87" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="U87" t="n">
         <v>8</v>
@@ -7499,15 +7495,19 @@
       <c r="V87" t="n">
         <v>29</v>
       </c>
-      <c r="W87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>5.3 (3g)</t>
+        </is>
+      </c>
       <c r="X87" t="n">
-        <v>-14.8</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7517,75 +7517,75 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="E88" t="n">
-        <v>16</v>
+        <v>13.3</v>
       </c>
       <c r="F88" t="n">
-        <v>15.8</v>
+        <v>12.4</v>
       </c>
       <c r="G88" t="n">
-        <v>15.8</v>
+        <v>13.5</v>
       </c>
       <c r="H88" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="I88" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="J88" t="n">
-        <v>23.6</v>
+        <v>30.9</v>
       </c>
       <c r="K88" t="n">
-        <v>22.4</v>
+        <v>28.3</v>
       </c>
       <c r="L88" t="n">
-        <v>73</v>
+        <v>42.4</v>
       </c>
       <c r="M88" t="n">
-        <v>62.7</v>
+        <v>42.2</v>
       </c>
       <c r="N88" t="n">
         <v>6.5</v>
       </c>
       <c r="O88" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="P88" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="Q88" t="n">
-        <v>-0.8</v>
+        <v>-2</v>
       </c>
       <c r="R88" t="n">
-        <v>5.1</v>
+        <v>-0.1</v>
       </c>
       <c r="S88" t="n">
-        <v>10.3</v>
+        <v>0.2</v>
       </c>
       <c r="T88" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="U88" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V88" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
-        <v>2</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7595,79 +7595,79 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E89" t="n">
-        <v>17.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F89" t="n">
-        <v>18.4</v>
+        <v>7.6</v>
       </c>
       <c r="G89" t="n">
-        <v>17.9</v>
+        <v>9.5</v>
       </c>
       <c r="H89" t="n">
-        <v>20.6</v>
+        <v>10.7</v>
       </c>
       <c r="I89" t="n">
-        <v>22.2</v>
+        <v>11.5</v>
       </c>
       <c r="J89" t="n">
-        <v>32.7</v>
+        <v>19.2</v>
       </c>
       <c r="K89" t="n">
-        <v>34.1</v>
+        <v>22.9</v>
       </c>
       <c r="L89" t="n">
-        <v>44.6</v>
+        <v>35.4</v>
       </c>
       <c r="M89" t="n">
-        <v>52.6</v>
+        <v>40.2</v>
       </c>
       <c r="N89" t="n">
-        <v>3.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O89" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P89" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="R89" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="T89" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S89" t="n">
-        <v>-8</v>
-      </c>
-      <c r="T89" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="U89" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="V89" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>20.0 (3g)</t>
+          <t>10.0 (7g)</t>
         </is>
       </c>
       <c r="X89" t="n">
-        <v>-4</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7677,79 +7677,75 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
       <c r="E90" t="n">
-        <v>3.7</v>
+        <v>18.3</v>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>22.6</v>
       </c>
       <c r="G90" t="n">
-        <v>8.800000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="H90" t="n">
-        <v>9.300000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="I90" t="n">
-        <v>11</v>
+        <v>21.5</v>
       </c>
       <c r="J90" t="n">
-        <v>28.6</v>
+        <v>34.4</v>
       </c>
       <c r="K90" t="n">
-        <v>29.5</v>
+        <v>32.9</v>
       </c>
       <c r="L90" t="n">
-        <v>44.3</v>
+        <v>46.4</v>
       </c>
       <c r="M90" t="n">
-        <v>39.9</v>
+        <v>44.4</v>
       </c>
       <c r="N90" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="O90" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P90" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
       <c r="R90" t="n">
-        <v>-4</v>
+        <v>1.1</v>
       </c>
       <c r="S90" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="T90" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="U90" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V90" t="n">
         <v>29</v>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>7.7 (3g)</t>
-        </is>
-      </c>
+      <c r="W90" t="inlineStr"/>
       <c r="X90" t="n">
-        <v>5</v>
+        <v>-14.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7759,79 +7755,79 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E91" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="F91" t="n">
-        <v>13.2</v>
+        <v>7</v>
       </c>
       <c r="G91" t="n">
-        <v>12.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>13.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="J91" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="K91" t="n">
-        <v>27.8</v>
+        <v>29.5</v>
       </c>
       <c r="L91" t="n">
-        <v>43.5</v>
+        <v>44.3</v>
       </c>
       <c r="M91" t="n">
-        <v>44.7</v>
+        <v>39.9</v>
       </c>
       <c r="N91" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O91" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P91" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="R91" t="n">
-        <v>2.1</v>
+        <v>-4</v>
       </c>
       <c r="S91" t="n">
-        <v>-1.2</v>
+        <v>4.4</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U91" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V91" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>9.3 (3g)</t>
+          <t>7.7 (3g)</t>
         </is>
       </c>
       <c r="X91" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7845,55 +7841,55 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>23.5</v>
+        <v>8.5</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F92" t="n">
-        <v>21</v>
+        <v>13.2</v>
       </c>
       <c r="G92" t="n">
-        <v>23</v>
+        <v>12.3</v>
       </c>
       <c r="H92" t="n">
-        <v>24.5</v>
+        <v>13.3</v>
       </c>
       <c r="I92" t="n">
-        <v>23</v>
+        <v>11.1</v>
       </c>
       <c r="J92" t="n">
-        <v>34.1</v>
+        <v>27.8</v>
       </c>
       <c r="K92" t="n">
-        <v>35.6</v>
+        <v>27.8</v>
       </c>
       <c r="L92" t="n">
-        <v>39.5</v>
+        <v>43.5</v>
       </c>
       <c r="M92" t="n">
-        <v>44.2</v>
+        <v>44.7</v>
       </c>
       <c r="N92" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="O92" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P92" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="Q92" t="n">
-        <v>-0.5</v>
+        <v>2.6</v>
       </c>
       <c r="R92" t="n">
-        <v>-2</v>
+        <v>2.1</v>
       </c>
       <c r="S92" t="n">
-        <v>-4.7</v>
+        <v>-1.2</v>
       </c>
       <c r="T92" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>19</v>
@@ -7901,91 +7897,91 @@
       <c r="V92" t="n">
         <v>2</v>
       </c>
-      <c r="W92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>9.3 (3g)</t>
+        </is>
+      </c>
       <c r="X92" t="n">
-        <v>2.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NOP @ SAC</t>
+          <t>ORL @ DAL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>14.5</v>
+        <v>23.5</v>
       </c>
       <c r="E93" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="F93" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G93" t="n">
-        <v>14.9</v>
+        <v>23</v>
       </c>
       <c r="H93" t="n">
-        <v>13.2</v>
+        <v>24.5</v>
       </c>
       <c r="I93" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J93" t="n">
-        <v>25.5</v>
+        <v>34.1</v>
       </c>
       <c r="K93" t="n">
-        <v>23.5</v>
+        <v>35.6</v>
       </c>
       <c r="L93" t="n">
-        <v>42.8</v>
+        <v>39.5</v>
       </c>
       <c r="M93" t="n">
-        <v>43</v>
+        <v>44.2</v>
       </c>
       <c r="N93" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="O93" t="n">
         <v>40</v>
       </c>
       <c r="P93" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="Q93" t="n">
         <v>-0.5</v>
       </c>
       <c r="R93" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="T93" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U93" t="n">
+        <v>19</v>
+      </c>
+      <c r="V93" t="n">
         <v>2</v>
       </c>
-      <c r="S93" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="T93" t="n">
-        <v>2</v>
-      </c>
-      <c r="U93" t="n">
-        <v>23</v>
-      </c>
-      <c r="V93" t="n">
-        <v>6</v>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>15.4 (5g)</t>
-        </is>
-      </c>
+      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
-        <v>-6.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="94">
@@ -8005,7 +8001,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="E94" t="n">
         <v>14.3</v>
@@ -8044,7 +8040,7 @@
         <v>30</v>
       </c>
       <c r="Q94" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="R94" t="n">
         <v>3.4</v>
@@ -8083,7 +8079,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="E95" t="n">
         <v>27.7</v>
@@ -8119,10 +8115,10 @@
         <v>60</v>
       </c>
       <c r="P95" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q95" t="n">
-        <v>-1.2</v>
+        <v>-2.2</v>
       </c>
       <c r="R95" t="n">
         <v>1.7</v>
@@ -8165,7 +8161,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="n">
         <v>9.699999999999999</v>
@@ -8198,13 +8194,13 @@
         <v>4.7</v>
       </c>
       <c r="O96" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P96" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q96" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="R96" t="n">
         <v>-1</v>
@@ -8325,7 +8321,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E98" t="n">
         <v>12.7</v>
@@ -8358,13 +8354,13 @@
         <v>4.5</v>
       </c>
       <c r="O98" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P98" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Q98" t="n">
-        <v>-2.6</v>
+        <v>-1.6</v>
       </c>
       <c r="R98" t="n">
         <v>0.9</v>
@@ -8403,7 +8399,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="E99" t="n">
         <v>17.3</v>
@@ -8436,13 +8432,13 @@
         <v>5.4</v>
       </c>
       <c r="O99" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P99" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R99" t="n">
         <v>-2.3</v>
@@ -8481,7 +8477,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="E100" t="n">
         <v>11.7</v>
@@ -8514,13 +8510,13 @@
         <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P100" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q100" t="n">
-        <v>-3.8</v>
+        <v>-4.8</v>
       </c>
       <c r="R100" t="n">
         <v>4.7</v>
@@ -8641,7 +8637,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="E102" t="n">
         <v>20</v>
@@ -8680,7 +8676,7 @@
         <v>45</v>
       </c>
       <c r="Q102" t="n">
-        <v>-1.9</v>
+        <v>-2.9</v>
       </c>
       <c r="R102" t="n">
         <v>5</v>
@@ -8864,6 +8860,166 @@
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Trey Murphy III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NOP @ SAC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E105" t="n">
+        <v>15</v>
+      </c>
+      <c r="F105" t="n">
+        <v>19</v>
+      </c>
+      <c r="G105" t="n">
+        <v>20</v>
+      </c>
+      <c r="H105" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="L105" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="M105" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O105" t="n">
+        <v>50</v>
+      </c>
+      <c r="P105" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R105" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U105" t="n">
+        <v>16</v>
+      </c>
+      <c r="V105" t="n">
+        <v>15</v>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>20.0 (6g)</t>
+        </is>
+      </c>
+      <c r="X105" t="n">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Dylan Cardwell</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NOP @ SAC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I106" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J106" t="n">
+        <v>17</v>
+      </c>
+      <c r="K106" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L106" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="M106" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="N106" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O106" t="n">
+        <v>40</v>
+      </c>
+      <c r="P106" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="T106" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="U106" t="n">
+        <v>25</v>
+      </c>
+      <c r="V106" t="n">
+        <v>6</v>
+      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="n">
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -8877,7 +9033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -8982,10 +9138,10 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.455</v>
+        <v>1.364</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -9006,7 +9162,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9015,10 +9171,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.518</v>
+        <v>0.535</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9027,17 +9183,17 @@
         <v>22.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Siakam's L30 average of 24.3 pts vs line of 22.5, works against the UNDER. His H2H avg of 20.6 pts is 3.7 below his season L30. Opponent ranks as strong defense (#8) with slow pace (#22). Mixed signal picture: 4/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 22.1 pts (0.4 pts below line; 51% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
+          <t>Siakam's L30 average of 24.3 pts vs line of 21.5, supports the OVER. His H2H avg of 20.6 pts is 3.7 below his season L30. Opponent ranks as strong defense (#8) with slow pace (#22). 6/10 signals agree — Volume, HR L30, HR L10 support over; Defense, H2H against. Projection model targets 22.1 pts (0.6 pts above line; 53% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -9059,23 +9215,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.537</v>
+        <v>0.577</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>21.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>2.85</v>
@@ -9085,7 +9241,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Ball has a H2H avg of 25.5 pts vs this opponent (+5.0 vs line) — supporting the OVER. His H2H avg of 25.5 pts is 5.4 above his season L30. Opponent ranks as below-average defense (#22) with moderate pace (#13). 5/10 signals agree — Context, Defense, H2H support over; Volume, HR L30 against. Projection model targets 21.9 pts (1.4 pts above line; 53% blended confidence). Risk: L3 has dropped to 16.0 (4.1 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Ball has a H2H avg of 25.5 pts vs this opponent (+6.0 vs line) — supporting the OVER. His H2H avg of 25.5 pts is 5.4 above his season L30. Opponent ranks as below-average defense (#22) with moderate pace (#13). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Min Trend dissent. Projection model targets 21.9 pts (2.4 pts above line; 57% blended confidence). Risk: L3 has dropped to 16.0 (4.1 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
@@ -9126,10 +9282,10 @@
         <v>0.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.455</v>
+        <v>1.357</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -9174,10 +9330,10 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -9203,23 +9359,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.646</v>
+        <v>0.63</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>2.65</v>
@@ -9229,7 +9385,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Toppin has a H2H avg of 6.0 pts vs this opponent (-4.5 vs line) — supporting the UNDER. His H2H avg of 6.0 pts is 4.8 below his season L30; His TS% shifts -19.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#22). 6/10 signals agree — HR L30, Context, Defense support under; Volume, HR L10 against. Projection model targets 4.5 pts (6.0 pts below line; 64% blended confidence).</t>
+          <t>Toppin has a H2H avg of 6.0 pts vs this opponent (-3.5 vs line) — supporting the UNDER. His H2H avg of 6.0 pts is 4.8 below his season L30; His TS% shifts -19.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#22). 5/10 signals agree — HR L30, Defense, H2H support under; Volume, HR L10 against. Projection model targets 4.5 pts (5.0 pts below line; 63% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9402,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9255,29 +9411,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.539</v>
+        <v>0.52</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Miller has a H2H avg of 23.5 pts vs this opponent (+4.0 vs line) — supporting the OVER. His H2H avg of 23.5 pts is 3.2 above his season L30; His TS% shifts +11.4% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#13). 8/10 signals agree (Volume, HR L30, Trend, Context among the strongest); HR L10, Min Trend dissent. Projection model targets 20.2 pts (0.7 pts above line; 53% blended confidence).</t>
+          <t>Miller has a H2H avg of 23.5 pts vs this opponent (+3.0 vs line) — working against the UNDER. His H2H avg of 23.5 pts is 3.2 above his season L30; His TS% shifts +11.4% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#13). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, Min Trend. Counter-signals: HR L30, HR L10, Trend. Projection model targets 20.1 pts (0.4 pts below line; 52% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9318,10 +9474,10 @@
         <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>1.364</v>
+        <v>1.4</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
@@ -9414,10 +9570,10 @@
         <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="K11" t="n">
-        <v>1.385</v>
+        <v>1.4</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -9476,7 +9632,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9486,7 +9642,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9495,7 +9651,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.649</v>
+        <v>0.595</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
@@ -9504,27 +9660,27 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7</v>
+        <v>18.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.746</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.01</v>
+        <v>1.385</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Jones's L30 average of 4.3 pts vs line of 6.5, supports the UNDER. FG% trend -5.7% (L10 vs L30). Opponent ranks as strong defense (#9) with slow pace (#22). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, Min Trend dissent. Projection model targets 1.7 pts (4.8 pts below line; 64% blended confidence).</t>
+          <t>White has a H2H avg of 19.4 pts vs this opponent (+3.9 vs line) — supporting the OVER. His H2H avg of 19.4 pts is 2.6 above his season L30; His TS% shifts -4.0% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#13). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Min Trend dissent. Projection model targets 18.2 pts (2.7 pts above line; 59% blended confidence). Risk: minutes trending down (20.9 L10 vs 24.5 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9534,7 +9690,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9543,29 +9699,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.552</v>
+        <v>0.681</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>18.2</v>
+        <v>1.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J14" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="K14" t="n">
-        <v>1.87</v>
+        <v>1.746</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>White has a H2H avg of 19.4 pts vs this opponent (+2.9 vs line) — supporting the OVER. His H2H avg of 19.4 pts is 2.6 above his season L30; His TS% shifts -4.0% in this matchup. Opponent ranks as below-average defense (#22) with moderate pace (#13). 7/10 signals agree (Volume, HR L10, Context, Defense among the strongest); HR L30, Trend dissent. Projection model targets 18.2 pts (1.7 pts above line; 55% blended confidence). Risk: minutes trending down (20.9 L10 vs 24.5 L30 — role reduction would suppress counting stats.</t>
+          <t>Jones's L30 average of 4.3 pts is 3.2 below the 7.5 line, supports the UNDER. FG% trend -5.7% (L10 vs L30). Opponent ranks as strong defense (#9) with slow pace (#22). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, Min Trend dissent. Projection model targets 1.7 pts (5.8 pts below line; 68% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9591,10 +9747,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.744</v>
+        <v>0.715</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -9603,17 +9759,17 @@
         <v>7.4</v>
       </c>
       <c r="I15" t="n">
-        <v>12.1</v>
+        <v>8.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="K15" t="n">
-        <v>1.385</v>
+        <v>1.455</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>George shows recent scoring up 7.6 pts vs L30 (L5 vs L30 trend). FG% trend +4.2% (L10 vs L30). Opponent ranks as strong defense (#7) with moderate pace (#16). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, H2H against. Projection model targets 7.4 pts (12.1 pts below line; 74% blended confidence). Risk: L3 has surged to 28.0 after a 19-pt performance (10.2 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>George shows recent scoring up 7.6 pts vs L30 (L5 vs L30 trend). FG% trend +4.2% (L10 vs L30). Opponent ranks as strong defense (#7) with moderate pace (#16). Mixed signal picture: 2/10 agree. Agreeing: Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 7.4 pts (8.1 pts below line; 71% blended confidence). Risk: L3 has surged to 28.0 after a 19-pt performance (10.2 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -9639,10 +9795,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.556</v>
+        <v>0.524</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -9651,17 +9807,17 @@
         <v>10.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1.364</v>
+        <v>1.599</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>DiVincenzo shows recent scoring up 2.6 pts vs L30 (L5 vs L30 trend). His TS% shifts +18.1% in this matchup; FG% trend -3.8% (L10 vs L30). Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 10.6 pts (1.9 pts below line; 55% blended confidence).</t>
+          <t>DiVincenzo shows recent scoring up 2.6 pts vs L30 (L5 vs L30 trend). His TS% shifts +18.1% in this matchup; FG% trend -3.8% (L10 vs L30). Opponent ranks as below-average defense (#16) with slow pace (#23). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 10.6 pts (0.9 pts below line; 52% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9702,10 +9858,10 @@
         <v>0.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9</v>
+        <v>1.769</v>
       </c>
       <c r="K17" t="n">
-        <v>1.385</v>
+        <v>1.952</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -9716,7 +9872,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Adem Bona</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9726,7 +9882,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9735,36 +9891,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>0.751</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>38.5</v>
       </c>
       <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.55</v>
-      </c>
       <c r="K18" t="n">
-        <v>1.476</v>
+        <v>1.364</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Bona has a H2H avg of 4.3 pts vs this opponent (-2.2 vs line) — supporting the UNDER. His H2H avg of 4.3 pts is 1.7 below his season L30; FG% trend -3.9% (L10 vs L30). Opponent ranks as strong defense (#7) with moderate pace (#16). 9/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Min Trend dissents. Projection model targets 3.5 pts (3.0 pts below line; 60% blended confidence).</t>
+          <t>Maxey's L30 average of 26.7 pts vs line of 26.5, supports the OVER. Opponent ranks as average defense (#14) with moderate pace (#16). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 38.5 pts (12.0 pts above line; 75% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9774,7 +9930,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -9783,19 +9939,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.756</v>
+        <v>0.538</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>38.6</v>
+        <v>27.1</v>
       </c>
       <c r="I19" t="n">
-        <v>10.1</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>2.9</v>
@@ -9805,7 +9961,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Maxey's L30 average of 26.7 pts vs line of 28.5, works against the OVER. Opponent ranks as average defense (#14) with moderate pace (#16). Mixed signal picture: 2/10 agree. Agreeing: FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 38.6 pts (10.1 pts above line; 75% blended confidence).</t>
+          <t>Embiid's L30 average of 28.3 pts vs line of 28.5, supports the UNDER. Opponent ranks as average defense (#13) with moderate pace (#16). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Defense. Counter-signals: HR L30, HR L10, Trend. Projection model targets 27.1 pts (1.4 pts below line; 53% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9987,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.593</v>
+        <v>0.582</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -9843,7 +9999,7 @@
         <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>2.9</v>
@@ -9853,7 +10009,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Barlow shows recent scoring down 3.3 pts vs L30 (L5 vs L30 trend). FG% trend +6.5% (L10 vs L30). Opponent ranks as strong defense (#7) with moderate pace (#16). Mixed signal picture: 4/10 agree. Agreeing: Trend, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 2.7 pts (3.8 pts below line; 59% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Barlow shows recent scoring down 3.3 pts vs L30 (L5 vs L30 trend). FG% trend +6.5% (L10 vs L30). Opponent ranks as strong defense (#7) with moderate pace (#16). Mixed signal picture: 4/10 agree. Agreeing: Trend, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 2.7 pts (2.8 pts below line; 58% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
@@ -9879,10 +10035,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.614</v>
+        <v>0.725</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9891,17 +10047,17 @@
         <v>17.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>8.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K21" t="n">
-        <v>1.364</v>
+        <v>1.417</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 average of 14.4 pts vs line of 12.5, supports the OVER. Opponent ranks as strong defense (#7) with moderate pace (#16). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 17.6 pts (5.1 pts above line; 61% blended confidence). Risk: high scoring volatility (σ=8.3) introduces outcome uncertainty.</t>
+          <t>Jr.'s L30 average of 14.4 pts is 4.9 above the 9.5 line, supports the OVER. Opponent ranks as strong defense (#7) with moderate pace (#16). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 17.6 pts (8.1 pts above line; 72% blended confidence). Risk: high scoring volatility (σ=8.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -9942,10 +10098,10 @@
         <v>7.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -10023,10 +10179,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.582</v>
+        <v>0.758</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -10035,17 +10191,17 @@
         <v>16.9</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.345</v>
+        <v>1.408</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Grimes has a H2H avg of 16.8 pts vs this opponent (+3.3 vs line) — supporting the OVER. His H2H avg of 16.8 pts is 3.2 above his season L30; His TS% shifts +13.6% in this matchup. Opponent ranks as average defense (#14) with moderate pace (#16). 6/10 signals agree — Volume, HR L30, Trend support over; HR L10, Defense against. Projection model targets 16.9 pts (3.4 pts above line; 58% blended confidence). Risk: high scoring volatility (σ=8.6) introduces outcome uncertainty.</t>
+          <t>Grimes has a H2H avg of 16.8 pts vs this opponent (+8.3 vs line) — supporting the OVER. His H2H avg of 16.8 pts is 3.2 above his season L30; His TS% shifts +13.6% in this matchup. Opponent ranks as average defense (#14) with moderate pace (#16). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 16.9 pts (8.4 pts above line; 75% blended confidence). Risk: high scoring volatility (σ=8.6) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10227,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.52</v>
+        <v>0.552</v>
       </c>
       <c r="F25" t="n">
         <v>6</v>
@@ -10083,17 +10239,17 @@
         <v>26.1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>1.364</v>
+        <v>1.333</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Edwards's L30 average of 29.1 pts is 3.6 above the 25.5 line, supports the OVER. His TS% shifts +8.9% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 26.1 pts (0.6 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=10.3) introduces outcome uncertainty.</t>
+          <t>Edwards's L30 average of 29.1 pts is 4.6 above the 24.5 line, supports the OVER. His TS% shifts +8.9% in this matchup. Opponent ranks as below-average defense (#16) with slow pace (#23). 6/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 26.1 pts (1.6 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=10.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -10134,10 +10290,10 @@
         <v>6.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -10167,7 +10323,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.754</v>
+        <v>0.787</v>
       </c>
       <c r="F27" t="n">
         <v>6</v>
@@ -10179,17 +10335,17 @@
         <v>24.8</v>
       </c>
       <c r="I27" t="n">
-        <v>9.300000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Edgecombe shows recent scoring up 4.4 pts vs L30 (L5 vs L30 trend). FG% trend +7.4% (L10 vs L30). Opponent ranks as average defense (#14) with moderate pace (#16). 6/10 signals agree — Volume, HR L30, HR L10 support over; Defense, H2H against. Projection model targets 24.8 pts (9.3 pts above line; 75% blended confidence). Risk: high scoring volatility (σ=9.4) introduces outcome uncertainty.</t>
+          <t>Edgecombe shows recent scoring up 4.4 pts vs L30 (L5 vs L30 trend). FG% trend +7.4% (L10 vs L30). Opponent ranks as average defense (#14) with moderate pace (#16). 6/10 signals agree — Volume, HR L30, HR L10 support over; Defense, H2H against. Projection model targets 24.8 pts (11.3 pts above line; 78% blended confidence). Risk: high scoring volatility (σ=9.4) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -10230,10 +10386,10 @@
         <v>0.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -10278,10 +10434,10 @@
         <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.417</v>
+        <v>1.345</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -10374,10 +10530,10 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>1.345</v>
+        <v>1.357</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -10407,10 +10563,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.537</v>
+        <v>0.573</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -10419,17 +10575,17 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Clowney shows recent scoring down 4.9 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.0 pts is 2.3 below his season L30; His TS% shifts +4.3% in this matchup. Opponent ranks as weak defense (#24) with above-average pace (#7). Mixed signal picture: 4/10 agree. Agreeing: Trend, H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.2 pts (1.3 pts below line; 53% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Clowney shows recent scoring down 4.9 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.0 pts is 2.3 below his season L30; His TS% shifts +4.3% in this matchup. Opponent ranks as weak defense (#24) with above-average pace (#7). 7/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, Defense dissent. Projection model targets 8.2 pts (2.3 pts below line; 57% blended confidence). Risk: minutes trending down (21.4 L10 vs 25.6 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -10470,10 +10626,10 @@
         <v>3.1</v>
       </c>
       <c r="J33" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.333</v>
+        <v>1.357</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -10518,10 +10674,10 @@
         <v>11.1</v>
       </c>
       <c r="J34" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>1.465</v>
+        <v>1.357</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -10566,10 +10722,10 @@
         <v>0.7</v>
       </c>
       <c r="J35" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="K35" t="n">
-        <v>1.417</v>
+        <v>1.435</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -10647,29 +10803,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.598</v>
+        <v>0.586</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J37" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="K37" t="n">
-        <v>1.357</v>
+        <v>1.435</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Daniels's L30 average of 12.1 pts vs line of 12.5, supports the UNDER. His H2H avg of 10.6 pts is 1.5 below his season L30; His TS% shifts -7.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#30). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 8.7 pts (3.8 pts below line; 59% blended confidence). Risk: high scoring volatility (σ=7.2) introduces outcome uncertainty.</t>
+          <t>Daniels's L30 average of 12.1 pts vs line of 11.5, works against the UNDER. His H2H avg of 10.6 pts is 1.5 below his season L30; His TS% shifts -7.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#30). Mixed signal picture: 3/10 agree. Agreeing: Context, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.8 pts (2.7 pts below line; 58% blended confidence). Risk: high scoring volatility (σ=7.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -10710,10 +10866,10 @@
         <v>3.1</v>
       </c>
       <c r="J38" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K38" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -10758,10 +10914,10 @@
         <v>2.8</v>
       </c>
       <c r="J39" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="K39" t="n">
-        <v>1.87</v>
+        <v>1.417</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -10791,29 +10947,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.619</v>
+        <v>0.631</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
-        <v>1.735</v>
+        <v>2.9</v>
       </c>
       <c r="K40" t="n">
-        <v>2.01</v>
+        <v>1.385</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Robinson shows low scoring variance (σ=3.4) — highly predictable output. FG% trend +3.0% (L10 vs L30). Opponent ranks as weak defense (#26) with fast pace (#1). Mixed signal picture: 1/10 agree. Agreeing: Context. Counter-signals: Volume, HR L30, HR L10. Projection model targets 1.9 pts (3.6 pts below line; 61% blended confidence).</t>
+          <t>Robinson shows low scoring variance (σ=3.4) — highly predictable output. FG% trend +3.0% (L10 vs L30). Opponent ranks as weak defense (#26) with fast pace (#1). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, HR L10. Counter-signals: Trend, Defense, H2H. Projection model targets 1.8 pts (4.7 pts below line; 63% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -10835,33 +10991,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.539</v>
+        <v>0.578</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>11.1</v>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1.952</v>
+        <v>2.8</v>
       </c>
       <c r="K41" t="n">
-        <v>1.8</v>
+        <v>1.408</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Okoro shows recent scoring up 2.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as strong defense (#8) with slow pace (#27). 6/10 signals agree — Volume, HR L30, Trend support over; HR L10, Defense against. Projection model targets 11.1 pts (1.6 pts above line; 53% blended confidence).</t>
+          <t>Okoro shows recent scoring up 2.0 pts vs L30 (L5 vs L30 trend). Opponent ranks as strong defense (#8) with slow pace (#27). 7/10 signals agree (Volume, HR L30, Trend, Context among the strongest); HR L10, Defense dissent. Projection model targets 11.1 pts (2.6 pts above line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -10883,33 +11039,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.705</v>
+        <v>0.67</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>5.7</v>
       </c>
       <c r="I42" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="K42" t="n">
-        <v>1.87</v>
+        <v>1.455</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Hart has a H2H avg of 6.6 pts vs this opponent (-6.9 vs line) — supporting the UNDER. His H2H avg of 6.6 pts is 5.7 below his season L30; His TS% shifts -7.3% in this matchup. Opponent ranks as below-average defense (#18) with fast pace (#1). 6/10 signals agree — Volume, HR L30, HR L10 support under; Defense, Pace against. Projection model targets 5.7 pts (7.8 pts below line; 70% blended confidence). Risk: high scoring volatility (σ=7.8) introduces outcome uncertainty.</t>
+          <t>Hart has a H2H avg of 6.6 pts vs this opponent (-5.9 vs line) — supporting the UNDER. His H2H avg of 6.6 pts is 5.7 below his season L30; His TS% shifts -7.3% in this matchup. Opponent ranks as below-average defense (#18) with fast pace (#1). 5/10 signals agree — Volume, HR L30, Trend support under; HR L10, Defense against. Projection model targets 5.7 pts (6.8 pts below line; 67% blended confidence). Risk: high scoring volatility (σ=7.8) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -10950,10 +11106,10 @@
         <v>1.7</v>
       </c>
       <c r="J43" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="K43" t="n">
-        <v>1.952</v>
+        <v>1.385</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -10998,10 +11154,10 @@
         <v>0.7</v>
       </c>
       <c r="J44" t="n">
-        <v>1.833</v>
+        <v>2.75</v>
       </c>
       <c r="K44" t="n">
-        <v>1.909</v>
+        <v>1.417</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -11046,10 +11202,10 @@
         <v>4.9</v>
       </c>
       <c r="J45" t="n">
-        <v>1.901</v>
+        <v>2.8</v>
       </c>
       <c r="K45" t="n">
-        <v>1.833</v>
+        <v>1.408</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -11094,10 +11250,10 @@
         <v>2.4</v>
       </c>
       <c r="J46" t="n">
-        <v>1.952</v>
+        <v>3.1</v>
       </c>
       <c r="K46" t="n">
-        <v>1.8</v>
+        <v>1.345</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -11142,10 +11298,10 @@
         <v>2.1</v>
       </c>
       <c r="J47" t="n">
-        <v>1.952</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>1.8</v>
+        <v>1.357</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -11190,10 +11346,10 @@
         <v>1.8</v>
       </c>
       <c r="J48" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="K48" t="n">
-        <v>1.952</v>
+        <v>1.345</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -11238,10 +11394,10 @@
         <v>2.4</v>
       </c>
       <c r="J49" t="n">
-        <v>1.952</v>
+        <v>2.9</v>
       </c>
       <c r="K49" t="n">
-        <v>1.8</v>
+        <v>1.385</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -11286,10 +11442,10 @@
         <v>6.1</v>
       </c>
       <c r="J50" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K50" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -11319,7 +11475,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.585</v>
+        <v>0.545</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -11331,7 +11487,7 @@
         <v>11.3</v>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>2.9</v>
@@ -11341,7 +11497,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Dieng shows recent scoring up 7.3 pts vs L30 (L5 vs L30 trend). FG% trend +3.1% (L10 vs L30). Opponent ranks as elite defense (#2) with slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, H2H against. Projection model targets 11.3 pts (2.2 pts below line; 58% blended confidence). Risk: L3 has surged to 18.0 (8.9 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Dieng shows recent scoring up 7.3 pts vs L30 (L5 vs L30 trend). FG% trend +3.1% (L10 vs L30). Opponent ranks as elite defense (#2) with slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, H2H against. Projection model targets 11.3 pts (1.2 pts below line; 54% blended confidence). Risk: L3 has surged to 18.0 (8.9 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -11382,10 +11538,10 @@
         <v>3.1</v>
       </c>
       <c r="J52" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -11430,10 +11586,10 @@
         <v>0.1</v>
       </c>
       <c r="J53" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K53" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -11463,10 +11619,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.6</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -11475,17 +11631,17 @@
         <v>8</v>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="K54" t="n">
-        <v>1.345</v>
+        <v>1.417</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 average of 7.1 pts is 4.4 below the 11.5 line, supports the UNDER. His H2H avg of 9.0 pts is 1.9 above his season L30; His TS% shifts +10.1% in this matchup. Opponent ranks as elite defense (#2) with slow pace (#24). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, FG Trend dissent. Projection model targets 8.0 pts (3.5 pts below line; 59% blended confidence). Risk: L3 has surged to 16.3 after a 13-pt performance (9.2 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Jr. shows recent scoring up 6.3 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.0 pts is 1.9 above his season L30; His TS% shifts +10.1% in this matchup. Opponent ranks as elite defense (#2) with slow pace (#24). 6/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 8.0 pts (2.5 pts below line; 56% blended confidence). Risk: L3 has surged to 16.3 after a 13-pt performance (9.2 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -11511,10 +11667,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.695</v>
+        <v>0.663</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -11523,17 +11679,17 @@
         <v>5.4</v>
       </c>
       <c r="I55" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K55" t="n">
-        <v>1.364</v>
+        <v>1.435</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Turner has a H2H avg of 7.4 pts vs this opponent (-4.1 vs line) — supporting the UNDER. His H2H avg of 7.4 pts is 4.0 below his season L30; His TS% shifts -14.4% in this matchup. Opponent ranks as elite defense (#1) with slow pace (#24). Full consensus: 10/10 signals align (Volume, HR L30, HR L10, Trend all agree). Projection model targets 5.4 pts (6.1 pts below line; 69% blended confidence).</t>
+          <t>Turner has a H2H avg of 7.4 pts vs this opponent (-3.1 vs line) — supporting the UNDER. His H2H avg of 7.4 pts is 4.0 below his season L30; His TS% shifts -14.4% in this matchup. Opponent ranks as elite defense (#1) with slow pace (#24). 9/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume dissents. Projection model targets 5.4 pts (5.1 pts below line; 66% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -11622,10 +11778,10 @@
         <v>2.8</v>
       </c>
       <c r="J57" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K57" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -11670,10 +11826,10 @@
         <v>4.6</v>
       </c>
       <c r="J58" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K58" t="n">
-        <v>1.357</v>
+        <v>1.345</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
@@ -11718,10 +11874,10 @@
         <v>0.2</v>
       </c>
       <c r="J59" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K59" t="n">
-        <v>1.357</v>
+        <v>1.333</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -11766,10 +11922,10 @@
         <v>4.2</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="K60" t="n">
-        <v>1.345</v>
+        <v>1.4</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
@@ -11799,10 +11955,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.548</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -11811,17 +11967,17 @@
         <v>16.2</v>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K61" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Thompson shows low scoring variance (σ=4.8) — highly predictable output. His H2H avg of 15.7 pts is 1.7 below his season L30; His TS% shifts +3.6% in this matchup. Opponent ranks as weak defense (#30) with above-average pace (#8). Mixed signal picture: 4/10 agree. Agreeing: Volume, Trend, Context. Counter-signals: HR L30, HR L10, Defense. Projection model targets 16.2 pts (1.3 pts below line; 54% blended confidence). Risk: 70% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Thompson has a H2H avg of 15.7 pts vs this opponent (-2.8 vs line) — supporting the UNDER. His H2H avg of 15.7 pts is 1.7 below his season L30; His TS% shifts +3.6% in this matchup. Opponent ranks as weak defense (#30) with above-average pace (#8). 5/10 signals agree — Volume, HR L10, Trend support under; HR L30, Defense against. Projection model targets 16.2 pts (2.3 pts below line; 55% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -11847,10 +12003,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.629</v>
+        <v>0.593</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -11859,17 +12015,17 @@
         <v>12.5</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K62" t="n">
-        <v>1.408</v>
+        <v>1.357</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Filipowski has a H2H avg of 11.2 pts vs this opponent (-5.3 vs line) — supporting the UNDER. His H2H avg of 11.2 pts is 2.9 below his season L30; His TS% shifts -10.5% in this matchup. Opponent ranks as strong defense (#7) with moderate pace (#20). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Min Trend dissent. Projection model targets 12.5 pts (4.0 pts below line; 62% blended confidence). Risk: L3 has surged to 23.7 after a 15-pt performance (9.6 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Filipowski shows recent scoring up 6.3 pts vs L30 (L5 vs L30 trend). His H2H avg of 11.2 pts is 2.9 below his season L30; His TS% shifts -10.5% in this matchup. Opponent ranks as strong defense (#7) with moderate pace (#20). 7/10 signals agree (Volume, HR L30, Context, Defense among the strongest); HR L10, Trend dissent. Projection model targets 12.5 pts (3.0 pts below line; 59% blended confidence). Risk: L3 has surged to 23.7 after a 15-pt performance (9.6 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -11910,10 +12066,10 @@
         <v>4.1</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K63" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
@@ -12006,10 +12162,10 @@
         <v>0.4</v>
       </c>
       <c r="J65" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K65" t="n">
-        <v>1.345</v>
+        <v>1.357</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -12039,29 +12195,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.599</v>
+        <v>0.635</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K66" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Sengun has a H2H avg of 24.8 pts vs this opponent (+4.3 vs line) — supporting the OVER. His H2H avg of 24.8 pts is 5.3 above his season L30; His TS% shifts +6.1% in this matchup. Opponent ranks as below-average defense (#22) with above-average pace (#8). 6/10 signals agree — Trend, Defense, H2H support over; Volume, HR L30 against. Projection model targets 24.2 pts (3.7 pts above line; 59% blended confidence). Risk: high scoring volatility (σ=9.2) introduces outcome uncertainty.</t>
+          <t>Sengun has a H2H avg of 24.8 pts vs this opponent (+5.3 vs line) — supporting the OVER. His H2H avg of 24.8 pts is 5.3 above his season L30; His TS% shifts +6.1% in this matchup. Opponent ranks as below-average defense (#22) with above-average pace (#8). 7/10 signals agree (Trend, Context, Defense, H2H among the strongest); Volume, HR L30 dissent. Projection model targets 24.5 pts (5.0 pts above line; 63% blended confidence). Risk: high scoring volatility (σ=9.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -12102,10 +12258,10 @@
         <v>0.6</v>
       </c>
       <c r="J67" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="K67" t="n">
-        <v>1.435</v>
+        <v>1.417</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -12150,10 +12306,10 @@
         <v>0.6</v>
       </c>
       <c r="J68" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K68" t="n">
-        <v>1.357</v>
+        <v>1.345</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -12198,10 +12354,10 @@
         <v>0.9</v>
       </c>
       <c r="J69" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K69" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -12246,10 +12402,10 @@
         <v>1.2</v>
       </c>
       <c r="J70" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="K70" t="n">
-        <v>1.435</v>
+        <v>1.345</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -12279,29 +12435,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.52</v>
+        <v>0.554</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K71" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Ingram shows recent scoring down 5.3 pts vs L30 (L5 vs L30 trend). Opponent ranks as weak defense (#23) with fast pace (#5). Mixed signal picture: 4/10 agree. Agreeing: HR L30, HR L10, Trend. Counter-signals: Volume, Defense, H2H. Projection model targets 19.4 pts (1.1 pts below line; 51% blended confidence). Risk: high scoring volatility (σ=9.6) introduces outcome uncertainty.</t>
+          <t>Ingram shows recent scoring down 5.3 pts vs L30 (L5 vs L30 trend). Opponent ranks as weak defense (#23) with fast pace (#5). 5/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 19.3 pts (2.2 pts below line; 55% blended confidence). Risk: high scoring volatility (σ=9.6) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -12342,10 +12498,10 @@
         <v>3.1</v>
       </c>
       <c r="J72" t="n">
-        <v>1.746</v>
+        <v>1.735</v>
       </c>
       <c r="K72" t="n">
-        <v>1.971</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
@@ -12438,10 +12594,10 @@
         <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K74" t="n">
-        <v>1.408</v>
+        <v>1.345</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
@@ -12510,19 +12666,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.519</v>
+        <v>0.531</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -12531,17 +12687,17 @@
         <v>8.6</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K76" t="n">
-        <v>1.435</v>
+        <v>1.364</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Shead shows recent scoring up 2.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with fast pace (#5). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 8.6 pts (0.1 pts above line; 51% blended confidence). Risk: L3 has surged to 11.3 after a 12-pt performance (5.7 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Shead shows recent scoring up 2.8 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#22) with fast pace (#5). Mixed signal picture: 4/10 agree. Agreeing: Trend, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.6 pts (1.1 pts above line; 53% blended confidence). Risk: only 35% hit rate over L30 — line may be set fairly.</t>
         </is>
       </c>
     </row>
@@ -12582,10 +12738,10 @@
         <v>2.7</v>
       </c>
       <c r="J77" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>1.417</v>
+        <v>1.364</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -12615,7 +12771,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.571</v>
+        <v>0.603</v>
       </c>
       <c r="F78" t="n">
         <v>7</v>
@@ -12627,7 +12783,7 @@
         <v>11.1</v>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>3</v>
@@ -12637,7 +12793,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Coward shows low scoring variance (σ=5.0) — highly predictable output. Opponent ranks as average defense (#13) with slow pace (#25). 7/10 signals agree (Volume, HR L30, Context, Defense among the strongest); HR L10, Trend dissent. Projection model targets 11.1 pts (2.4 pts below line; 57% blended confidence).</t>
+          <t>Coward shows low scoring variance (σ=5.0) — highly predictable output. Opponent ranks as average defense (#13) with slow pace (#25). 7/10 signals agree (Volume, HR L30, Context, Defense among the strongest); HR L10, Trend dissent. Projection model targets 11.1 pts (3.4 pts below line; 60% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -12678,10 +12834,10 @@
         <v>2.1</v>
       </c>
       <c r="J79" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="K79" t="n">
-        <v>1.435</v>
+        <v>1.417</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -12726,10 +12882,10 @@
         <v>2.2</v>
       </c>
       <c r="J80" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="K80" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -12740,7 +12896,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12755,40 +12911,40 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.575</v>
+        <v>0.615</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>12.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K81" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Wagner shows recent scoring down 8.4 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#19) with fast pace (#2). Mixed signal picture: 3/10 agree. Agreeing: Trend, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 12.4 pts (2.1 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=8.5) introduces outcome uncertainty.</t>
+          <t>Williams shows recent scoring down 3.6 pts vs L30 (L5 vs L30 trend). FG% trend -6.1% (L10 vs L30). Opponent ranks as below-average defense (#18) with slow pace (#29). 6/10 signals agree — HR L10, Trend, Context support under; Volume, HR L30 against. Projection model targets 9.7 pts (3.8 pts below line; 61% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12798,45 +12954,45 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.577</v>
+        <v>0.533</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>9.699999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J82" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K82" t="n">
-        <v>1.357</v>
+        <v>1.345</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Williams shows recent scoring down 3.6 pts vs L30 (L5 vs L30 trend). FG% trend -6.1% (L10 vs L30). Opponent ranks as below-average defense (#18) with slow pace (#29). 5/10 signals agree — HR L10, Trend, Pace support under; Volume, HR L30 against. Projection model targets 9.7 pts (2.8 pts below line; 57% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>[Low conviction — lean only] Jr. shows low scoring variance (σ=3.9) — highly predictable output. His TS% shifts +10.0% in this matchup; FG% trend +3.4% (L10 vs L30). Opponent ranks as weak defense (#27) with fast pace (#2). 8/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, H2H dissent. Projection model targets 11.4 pts (0.1 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -12846,45 +13002,45 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.522</v>
+        <v>0.597</v>
       </c>
       <c r="F83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>9.199999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="K83" t="n">
-        <v>1.455</v>
+        <v>1.364</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Middleton shows recent scoring down 3.9 pts vs L30 (L5 vs L30 trend). His H2H avg of 10.0 pts is 1.5 below his season L30; His TS% shifts -3.1% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 7/10 signals agree (HR L30, HR L10, Trend, Defense among the strongest); Volume, Context dissent. Projection model targets 9.2 pts (0.3 pts below line; 52% blended confidence). Risk: high scoring volatility (σ=9.3) introduces outcome uncertainty.</t>
+          <t>Gafford shows recent scoring up 5.1 pts vs L30 (L5 vs L30 trend). FG% trend +10.3% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#29). 5/10 signals agree — HR L10, Trend, Context support over; Volume, HR L30 against. Projection model targets 15.1 pts (3.6 pts above line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -12894,7 +13050,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12903,36 +13059,36 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.746</v>
+        <v>0.524</v>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>6.3</v>
+        <v>21</v>
       </c>
       <c r="I84" t="n">
-        <v>11.2</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K84" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>Marshall has a H2H avg of 5.3 pts vs this opponent (-12.2 vs line) — supporting the UNDER. His H2H avg of 5.3 pts is 12.5 below his season L30; His TS% shifts -19.7% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 6/10 signals agree — HR L30, Context, Defense support under; Volume, HR L10 against. Projection model targets 6.3 pts (11.2 pts below line; 74% blended confidence). Risk: high scoring volatility (σ=9.1) introduces outcome uncertainty.</t>
+          <t>Bane shows recent scoring down 3.8 pts vs L30 (L5 vs L30 trend). His H2H avg of 20.0 pts is 2.2 below his season L30; His TS% shifts -4.0% in this matchup. Opponent ranks as below-average defense (#21) with fast pace (#2). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Defense. Counter-signals: HR L30, HR L10, Trend. Projection model targets 21.0 pts (0.5 pts above line; 52% blended confidence). Risk: L3 has dropped to 17.3 (4.9 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -12942,7 +13098,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12951,36 +13107,36 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.617</v>
+        <v>0.549</v>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K85" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Suggs's L30 average of 12.5 pts vs line of 14.5, supports the UNDER. Opponent ranks as below-average defense (#21) with fast pace (#2). 5/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 10.5 pts (4.0 pts below line; 61% blended confidence).</t>
+          <t>Thompson has a H2H avg of 15.0 pts vs this opponent (+5.5 vs line) — supporting the OVER. His H2H avg of 15.0 pts is 2.9 above his season L30; His TS% shifts +14.1% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Defense. Counter-signals: HR L30, HR L10, Trend. Projection model targets 11.0 pts (1.5 pts above line; 54% blended confidence). Risk: L3 has dropped to 6.7 (5.4 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -12990,45 +13146,45 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.533</v>
+        <v>0.597</v>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>11.4</v>
+        <v>12.4</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K86" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Jr. shows low scoring variance (σ=3.9) — highly predictable output. His TS% shifts +10.0% in this matchup; FG% trend +3.4% (L10 vs L30). Opponent ranks as weak defense (#27) with fast pace (#2). 8/10 signals agree (HR L30, HR L10, Trend, Context among the strongest); Volume, H2H dissent. Projection model targets 11.4 pts (0.1 pts below line; 53% blended confidence).</t>
+          <t>Wagner shows recent scoring down 8.4 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#19) with fast pace (#2). Mixed signal picture: 3/10 agree. Agreeing: Trend, FG Trend, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 12.4 pts (3.1 pts below line; 59% blended confidence). Risk: high scoring volatility (σ=8.5) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -13047,36 +13203,36 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.634</v>
+        <v>0.732</v>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>18.8</v>
+        <v>6.1</v>
       </c>
       <c r="I87" t="n">
-        <v>4.7</v>
+        <v>10.4</v>
       </c>
       <c r="J87" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K87" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Flagg's L30 average of 21.5 pts vs line of 23.5, supports the UNDER. Opponent ranks as strong defense (#8) with slow pace (#29). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 18.8 pts (4.7 pts below line; 63% blended confidence).</t>
+          <t>Marshall has a H2H avg of 5.3 pts vs this opponent (-11.2 vs line) — supporting the UNDER. His H2H avg of 5.3 pts is 12.5 below his season L30; His TS% shifts -19.7% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). Mixed signal picture: 4/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 6.1 pts (10.4 pts below line; 73% blended confidence). Risk: high scoring volatility (σ=9.1) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -13086,7 +13242,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -13095,7 +13251,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.597</v>
+        <v>0.617</v>
       </c>
       <c r="F88" t="n">
         <v>5</v>
@@ -13104,27 +13260,27 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>15.1</v>
+        <v>10.5</v>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K88" t="n">
-        <v>1.417</v>
+        <v>1.4</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Gafford shows recent scoring up 5.1 pts vs L30 (L5 vs L30 trend). FG% trend +10.3% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#29). 5/10 signals agree — HR L10, Trend, Context support over; Volume, HR L30 against. Projection model targets 15.1 pts (3.6 pts above line; 59% blended confidence).</t>
+          <t>Suggs's L30 average of 12.5 pts vs line of 14.5, supports the UNDER. Opponent ranks as below-average defense (#21) with fast pace (#2). 5/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 10.5 pts (4.0 pts below line; 61% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -13134,45 +13290,45 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.54</v>
+        <v>0.522</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="K89" t="n">
-        <v>1.417</v>
+        <v>1.435</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>Bane shows recent scoring down 3.8 pts vs L30 (L5 vs L30 trend). His H2H avg of 20.0 pts is 2.2 below his season L30; His TS% shifts -4.0% in this matchup. Opponent ranks as below-average defense (#21) with fast pace (#2). 5/10 signals agree — Volume, Context, Defense support over; HR L30, HR L10 against. Projection model targets 21.0 pts (1.5 pts above line; 54% blended confidence). Risk: L3 has dropped to 17.3 (4.9 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>[Low conviction — lean only] Middleton shows recent scoring down 3.9 pts vs L30 (L5 vs L30 trend). His H2H avg of 10.0 pts is 1.5 below his season L30; His TS% shifts -3.1% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#29). 7/10 signals agree (HR L30, HR L10, Trend, Defense among the strongest); Volume, Context dissent. Projection model targets 9.2 pts (0.3 pts below line; 52% blended confidence). Risk: high scoring volatility (σ=9.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -13191,36 +13347,36 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.598</v>
+        <v>0.634</v>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>7</v>
+        <v>18.8</v>
       </c>
       <c r="I90" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J90" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K90" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Christie shows recent scoring down 4.0 pts vs L30 (L5 vs L30 trend). His H2H avg of 7.7 pts is 3.3 below his season L30; His TS% shifts +5.0% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). 6/10 signals agree — HR L10, Trend, Context support under; Volume, HR L30 against. Projection model targets 7.0 pts (3.5 pts below line; 59% blended confidence).</t>
+          <t>Flagg's L30 average of 21.5 pts vs line of 23.5, supports the UNDER. Opponent ranks as strong defense (#8) with slow pace (#29). 5/10 signals agree — Volume, HR L30, Context support under; HR L10, Trend against. Projection model targets 18.8 pts (4.7 pts below line; 63% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -13230,45 +13386,45 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.594</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>10.4</v>
+        <v>7</v>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K91" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Silva shows recent scoring up 2.1 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.3 pts is 1.8 below his season L30; His TS% shifts +17.0% in this matchup. Opponent ranks as below-average defense (#19) with fast pace (#2). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); FG Trend, Min Trend dissent. Projection model targets 10.4 pts (1.9 pts above line; 59% blended confidence).</t>
+          <t>Christie shows recent scoring down 4.0 pts vs L30 (L5 vs L30 trend). His H2H avg of 7.7 pts is 3.3 below his season L30; His TS% shifts +5.0% in this matchup. Opponent ranks as below-average defense (#18) with slow pace (#29). 5/10 signals agree — HR L10, Trend, H2H support under; Volume, HR L30 against. Projection model targets 7.0 pts (2.5 pts below line; 56% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -13278,86 +13434,86 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.498</v>
+        <v>0.594</v>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>23.6</v>
+        <v>10.4</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K92" t="n">
-        <v>1.333</v>
+        <v>1.357</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Banchero shows recent scoring down 2.0 pts vs L30 (L5 vs L30 trend). FG% trend -4.7% (L10 vs L30). Opponent ranks as below-average defense (#19) with fast pace (#2). 6/10 signals agree — Volume, HR L10, Trend support under; HR L30, Defense against. Projection model targets 23.6 pts (0.1 pts above line; 49% blended confidence). Risk: high scoring volatility (σ=10.5) introduces outcome uncertainty.</t>
+          <t>Silva shows recent scoring up 2.1 pts vs L30 (L5 vs L30 trend). His H2H avg of 9.3 pts is 1.8 below his season L30; His TS% shifts +17.0% in this matchup. Opponent ranks as below-average defense (#19) with fast pace (#2). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); FG Trend, Min Trend dissent. Projection model targets 10.4 pts (1.9 pts above line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NOP @ SAC</t>
+          <t>ORL @ DAL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.525</v>
+        <v>0.498</v>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>13.2</v>
+        <v>23.6</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
-        <v>1.787</v>
+        <v>2.9</v>
       </c>
       <c r="K93" t="n">
-        <v>1.935</v>
+        <v>1.385</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>Monk shows recent scoring up 2.0 pts vs L30 (L5 vs L30 trend). His TS% shifts -6.2% in this matchup. Opponent ranks as weak defense (#23) with above-average pace (#6). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 13.2 pts (1.3 pts below line; 52% blended confidence). Risk: high scoring volatility (σ=9.8) introduces outcome uncertainty.</t>
+          <t>[Low conviction — lean only] Banchero shows recent scoring down 2.0 pts vs L30 (L5 vs L30 trend). FG% trend -4.7% (L10 vs L30). Opponent ranks as below-average defense (#19) with fast pace (#2). 6/10 signals agree — Volume, HR L10, Trend support under; HR L30, Defense against. Projection model targets 23.6 pts (0.1 pts above line; 49% blended confidence). Risk: high scoring volatility (σ=10.5) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -13374,16 +13530,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.53</v>
+        <v>0.513</v>
       </c>
       <c r="F94" t="n">
         <v>5</v>
@@ -13395,17 +13551,17 @@
         <v>14.8</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J94" t="n">
-        <v>2.1</v>
+        <v>1.806</v>
       </c>
       <c r="K94" t="n">
-        <v>1.667</v>
+        <v>1.909</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Fears's L30 average of 12.0 pts is 3.5 below the 15.5 line, supports the UNDER. FG% trend +5.1% (L10 vs L30). Opponent ranks as weak defense (#25) with moderate pace (#15). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 14.8 pts (0.7 pts below line; 53% blended confidence).</t>
+          <t>[Low conviction — lean only] Fears shows recent scoring up 3.4 pts vs L30 (L5 vs L30 trend). FG% trend +5.1% (L10 vs L30). Opponent ranks as weak defense (#25) with moderate pace (#15). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 14.8 pts (0.3 pts above line; 51% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13587,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="F95" t="n">
         <v>4</v>
@@ -13443,17 +13599,17 @@
         <v>16.7</v>
       </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
-        <v>1.719</v>
+        <v>1.599</v>
       </c>
       <c r="K95" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>DeRozan's L30 average of 18.3 pts vs line of 19.5, supports the UNDER. His TS% shifts -6.8% in this matchup; FG% trend +4.7% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#6). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 16.7 pts (2.8 pts below line; 56% blended confidence). Risk: L3 has surged to 27.7 after a 20-pt performance (9.4 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>DeRozan has a H2H avg of 17.8 pts vs this opponent (-2.7 vs line) — supporting the UNDER. His TS% shifts -6.8% in this matchup; FG% trend +4.7% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#6). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 16.7 pts (3.8 pts below line; 57% blended confidence). Risk: L3 has surged to 27.7 after a 20-pt performance (9.4 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13635,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.518</v>
+        <v>0.556</v>
       </c>
       <c r="F96" t="n">
         <v>5</v>
@@ -13491,17 +13647,17 @@
         <v>10.8</v>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
-        <v>1.637</v>
+        <v>1.885</v>
       </c>
       <c r="K96" t="n">
-        <v>2.14</v>
+        <v>1.826</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>Clifford shows low scoring variance (σ=4.7) — highly predictable output. Opponent ranks as weak defense (#23) with above-average pace (#6). 5/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 10.8 pts (0.7 pts below line; 51% blended confidence).</t>
+          <t>Clifford shows low scoring variance (σ=4.7) — highly predictable output. Opponent ranks as weak defense (#23) with above-average pace (#6). 5/10 signals agree — Volume, HR L30, HR L10 support under; Defense, H2H against. Projection model targets 10.8 pts (1.7 pts below line; 55% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -13542,10 +13698,10 @@
         <v>3.9</v>
       </c>
       <c r="J97" t="n">
-        <v>1.676</v>
+        <v>1.746</v>
       </c>
       <c r="K97" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
@@ -13575,7 +13731,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.637</v>
+        <v>0.599</v>
       </c>
       <c r="F98" t="n">
         <v>6</v>
@@ -13587,17 +13743,17 @@
         <v>7.6</v>
       </c>
       <c r="I98" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
-        <v>2.16</v>
+        <v>1.775</v>
       </c>
       <c r="K98" t="n">
-        <v>1.629</v>
+        <v>1.943</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Queen shows low scoring variance (σ=4.5) — highly predictable output. FG% trend -3.7% (L10 vs L30). Opponent ranks as weak defense (#29) with moderate pace (#15). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 7.6 pts (4.9 pts below line; 63% blended confidence).</t>
+          <t>Queen shows low scoring variance (σ=4.5) — highly predictable output. FG% trend -3.7% (L10 vs L30). Opponent ranks as weak defense (#29) with moderate pace (#15). 6/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 7.6 pts (3.9 pts below line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -13623,10 +13779,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.553</v>
+        <v>0.575</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -13635,17 +13791,17 @@
         <v>16.7</v>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J99" t="n">
-        <v>1.917</v>
+        <v>1.971</v>
       </c>
       <c r="K99" t="n">
-        <v>1.8</v>
+        <v>1.746</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Bey shows recent scoring down 2.3 pts vs L30 (L5 vs L30 trend). Opponent ranks as weak defense (#25) with moderate pace (#15). Mixed signal picture: 1/10 agree. Agreeing: Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 16.7 pts (1.8 pts below line; 55% blended confidence).</t>
+          <t>Bey shows recent scoring down 2.3 pts vs L30 (L5 vs L30 trend). Opponent ranks as weak defense (#25) with moderate pace (#15). Mixed signal picture: 4/10 agree. Agreeing: HR L30, HR L10, Trend. Counter-signals: Volume, Defense, H2H. Projection model targets 16.7 pts (2.8 pts below line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -13671,10 +13827,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.548</v>
+        <v>0.513</v>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -13683,17 +13839,17 @@
         <v>13.8</v>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
-        <v>1.806</v>
+        <v>1.599</v>
       </c>
       <c r="K100" t="n">
-        <v>1.909</v>
+        <v>2.2</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Carter shows recent scoring up 4.7 pts vs L30 (L5 vs L30 trend). FG% trend +6.4% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#6). 6/10 signals agree — HR L10, Trend, Defense support over; Volume, HR L30 against. Projection model targets 13.8 pts (1.3 pts above line; 54% blended confidence). Risk: high scoring volatility (σ=8.0) introduces outcome uncertainty.</t>
+          <t>Carter shows recent scoring up 4.7 pts vs L30 (L5 vs L30 trend). FG% trend +6.4% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#6). 5/10 signals agree — Trend, Defense, Pace support over; Volume, HR L30 against. Projection model targets 13.8 pts (0.3 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=8.0) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -13734,10 +13890,10 @@
         <v>2.5</v>
       </c>
       <c r="J101" t="n">
-        <v>1.885</v>
+        <v>1.82</v>
       </c>
       <c r="K101" t="n">
-        <v>1.833</v>
+        <v>1.893</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
@@ -13767,7 +13923,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.611</v>
+        <v>0.578</v>
       </c>
       <c r="F102" t="n">
         <v>5</v>
@@ -13779,17 +13935,17 @@
         <v>18.6</v>
       </c>
       <c r="I102" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
-        <v>1.676</v>
+        <v>1.806</v>
       </c>
       <c r="K102" t="n">
-        <v>2.08</v>
+        <v>1.909</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Achiuwa shows recent scoring up 5.0 pts vs L30 (L5 vs L30 trend). His TS% shifts +10.3% in this matchup; FG% trend +5.6% (L10 vs L30). Opponent ranks as below-average defense (#22) with above-average pace (#6). 5/10 signals agree — Trend, Defense, Pace support over; Volume, HR L30 against. Projection model targets 18.6 pts (4.1 pts above line; 61% blended confidence).</t>
+          <t>Achiuwa shows recent scoring up 5.0 pts vs L30 (L5 vs L30 trend). His TS% shifts +10.3% in this matchup; FG% trend +5.6% (L10 vs L30). Opponent ranks as below-average defense (#22) with above-average pace (#6). 5/10 signals agree — Trend, Defense, Pace support over; Volume, HR L30 against. Projection model targets 18.6 pts (3.1 pts above line; 57% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -13878,14 +14034,110 @@
         <v>1.5</v>
       </c>
       <c r="J104" t="n">
-        <v>1.599</v>
+        <v>1.719</v>
       </c>
       <c r="K104" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
           <t>Raynaud shows recent scoring down 2.4 pts vs L30 (L5 vs L30 trend). Opponent ranks as weak defense (#25) with above-average pace (#6). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, H2H dissent. Projection model targets 16.0 pts (1.5 pts above line; 55% blended confidence). Risk: high scoring volatility (σ=8.9) introduces outcome uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Trey Murphy III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NOP @ SAC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>III shows recent scoring down 3.1 pts vs L30 (L5 vs L30 trend). His H2H avg of 20.0 pts is 2.1 below his season L30; His TS% shifts -4.9% in this matchup. Opponent ranks as below-average defense (#16) with moderate pace (#15). 5/10 signals agree — HR L30, Trend, Context support under; Volume, HR L10 against. Projection model targets 18.6 pts (2.9 pts below line; 57% blended confidence).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Dylan Cardwell</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NOP @ SAC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Cardwell shows low scoring variance (σ=2.7) — highly predictable output. FG% trend -6.2% (L10 vs L30). Opponent ranks as weak defense (#25) with above-average pace (#6). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 5.0 pts (0.5 pts above line; 52% blended confidence). Risk: minutes trending down (17.0 L10 vs 20.9 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -13900,7 +14152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13988,11 +14240,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="4">
@@ -14012,7 +14264,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="5">
@@ -14072,7 +14324,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
@@ -14088,11 +14340,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="9">
@@ -14178,7 +14430,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kam Jones</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -14188,17 +14440,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Kam Jones</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -14208,11 +14460,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -14232,7 +14484,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="16">
@@ -14252,7 +14504,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="17">
@@ -14278,7 +14530,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Adem Bona</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -14288,17 +14540,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -14308,7 +14560,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -14332,7 +14584,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="21">
@@ -14352,7 +14604,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
@@ -14412,7 +14664,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -14432,7 +14684,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="26">
@@ -14472,7 +14724,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="28">
@@ -14572,7 +14824,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="33">
@@ -14672,7 +14924,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="38">
@@ -14732,7 +14984,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="41">
@@ -14752,7 +15004,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="42">
@@ -14772,7 +15024,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="43">
@@ -14952,7 +15204,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="52">
@@ -15012,7 +15264,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55">
@@ -15032,7 +15284,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="56">
@@ -15152,7 +15404,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="62">
@@ -15172,7 +15424,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="63">
@@ -15252,7 +15504,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="67">
@@ -15352,7 +15604,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="72">
@@ -15448,11 +15700,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="77">
@@ -15492,7 +15744,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="79">
@@ -15538,7 +15790,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Brandon Williams</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -15552,13 +15804,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Brandon Williams</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -15568,17 +15820,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Khris Middleton</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -15588,17 +15840,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -15608,17 +15860,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -15628,17 +15880,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -15648,17 +15900,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cooper Flagg</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -15672,13 +15924,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>23.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -15688,17 +15940,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Khris Middleton</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -15708,17 +15960,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -15732,13 +15984,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -15748,17 +16000,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -15768,31 +16020,31 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>23.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NOP @ SAC</t>
+          <t>ORL @ DAL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>14.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="94">
@@ -15808,11 +16060,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="95">
@@ -15832,7 +16084,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="96">
@@ -15852,7 +16104,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="97">
@@ -15892,7 +16144,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="99">
@@ -15912,7 +16164,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="100">
@@ -15932,7 +16184,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="101">
@@ -15972,7 +16224,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="103">
@@ -16013,6 +16265,46 @@
       </c>
       <c r="D104" t="n">
         <v>14.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Trey Murphy III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NOP @ SAC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Dylan Cardwell</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NOP @ SAC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-03.xlsx
+++ b/daily/2026-04-03.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
         <bgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+        <bgColor rgb="0022C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -66,6 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1613,7 +1627,6 @@
       <c r="V14" t="n">
         <v>22</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>6.5</v>
       </c>
@@ -1691,7 +1704,6 @@
       <c r="V15" t="n">
         <v>16</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>-22.4</v>
       </c>
@@ -1843,7 +1855,7 @@
         <v>-1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>15</v>
@@ -1851,7 +1863,6 @@
       <c r="V17" t="n">
         <v>23</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>-0.6</v>
       </c>
@@ -1929,7 +1940,6 @@
       <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>7.4</v>
       </c>
@@ -2007,7 +2017,6 @@
       <c r="V19" t="n">
         <v>16</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -2085,7 +2094,6 @@
       <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>-18.7</v>
       </c>
@@ -2163,7 +2171,6 @@
       <c r="V21" t="n">
         <v>16</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>2.5</v>
       </c>
@@ -2241,7 +2248,6 @@
       <c r="V22" t="n">
         <v>23</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>22.7</v>
       </c>
@@ -2390,7 +2396,7 @@
         <v>0.2</v>
       </c>
       <c r="S24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>3.1</v>
@@ -2639,7 +2645,7 @@
         <v>7.4</v>
       </c>
       <c r="T27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>14</v>
@@ -2647,7 +2653,6 @@
       <c r="V27" t="n">
         <v>16</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>8.5</v>
       </c>
@@ -2889,7 +2894,6 @@
       <c r="V30" t="n">
         <v>7</v>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -3213,7 +3217,6 @@
       <c r="V34" t="n">
         <v>30</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-35.5</v>
       </c>
@@ -3291,7 +3294,6 @@
       <c r="V35" t="n">
         <v>7</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>-10.8</v>
       </c>
@@ -3369,7 +3371,6 @@
       <c r="V36" t="n">
         <v>7</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>4.6</v>
       </c>
@@ -3693,7 +3694,6 @@
       <c r="V40" t="n">
         <v>1</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-32.2</v>
       </c>
@@ -4591,7 +4591,6 @@
       <c r="V51" t="n">
         <v>24</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>19.6</v>
       </c>
@@ -5800,7 +5799,7 @@
         <v>40</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>4.1</v>
@@ -6227,7 +6226,6 @@
       <c r="V71" t="n">
         <v>5</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>17.3</v>
       </c>
@@ -6305,7 +6303,6 @@
       <c r="V72" t="n">
         <v>25</v>
       </c>
-      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>21.9</v>
       </c>
@@ -6383,7 +6380,6 @@
       <c r="V73" t="n">
         <v>25</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>0</v>
       </c>
@@ -6461,7 +6457,6 @@
       <c r="V74" t="n">
         <v>5</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>-4.6</v>
       </c>
@@ -6539,7 +6534,6 @@
       <c r="V75" t="n">
         <v>5</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>5.8</v>
       </c>
@@ -6617,7 +6611,6 @@
       <c r="V76" t="n">
         <v>5</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>25.5</v>
       </c>
@@ -6777,7 +6770,6 @@
       <c r="V78" t="n">
         <v>25</v>
       </c>
-      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>2.7</v>
       </c>
@@ -6937,7 +6929,6 @@
       <c r="V80" t="n">
         <v>5</v>
       </c>
-      <c r="W80" t="inlineStr"/>
       <c r="X80" t="n">
         <v>0</v>
       </c>
@@ -7015,7 +7006,6 @@
       <c r="V81" t="n">
         <v>29</v>
       </c>
-      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>-1.7</v>
       </c>
@@ -7175,7 +7165,6 @@
       <c r="V83" t="n">
         <v>29</v>
       </c>
-      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
         <v>2</v>
       </c>
@@ -7417,7 +7406,6 @@
       <c r="V86" t="n">
         <v>2</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>-13.1</v>
       </c>
@@ -7577,7 +7565,6 @@
       <c r="V88" t="n">
         <v>2</v>
       </c>
-      <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
         <v>-7.8</v>
       </c>
@@ -7737,7 +7724,6 @@
       <c r="V90" t="n">
         <v>29</v>
       </c>
-      <c r="W90" t="inlineStr"/>
       <c r="X90" t="n">
         <v>-14.8</v>
       </c>
@@ -7979,7 +7965,6 @@
       <c r="V93" t="n">
         <v>2</v>
       </c>
-      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
         <v>2.2</v>
       </c>
@@ -8057,7 +8042,6 @@
       <c r="V94" t="n">
         <v>15</v>
       </c>
-      <c r="W94" t="inlineStr"/>
       <c r="X94" t="n">
         <v>6.2</v>
       </c>
@@ -8217,7 +8201,6 @@
       <c r="V96" t="n">
         <v>6</v>
       </c>
-      <c r="W96" t="inlineStr"/>
       <c r="X96" t="n">
         <v>-11.2</v>
       </c>
@@ -8377,7 +8360,6 @@
       <c r="V98" t="n">
         <v>15</v>
       </c>
-      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
         <v>-0.2</v>
       </c>
@@ -8447,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>25</v>
@@ -8455,7 +8437,6 @@
       <c r="V99" t="n">
         <v>15</v>
       </c>
-      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -8533,7 +8514,6 @@
       <c r="V100" t="n">
         <v>6</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="n">
         <v>4.5</v>
       </c>
@@ -8857,7 +8837,6 @@
       <c r="V104" t="n">
         <v>6</v>
       </c>
-      <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
         <v>3</v>
       </c>
@@ -9017,7 +8996,6 @@
       <c r="V106" t="n">
         <v>6</v>
       </c>
-      <c r="W106" t="inlineStr"/>
       <c r="X106" t="n">
         <v>1.7</v>
       </c>
@@ -14208,183 +14186,417 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (16 pts vs 10.5 line, +5.5). Projection model targeted 7.5 pts (correct direction) but actual was 16. Likely shooting variance — per-minute output may have been on pace.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (30 pts vs 21.5 line, +8.5).</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (18 pts vs 19.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Ben Sheppard</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (7 pts vs 7.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (20 pts vs 17.5 line, +2.5). Projection model called 22.5 pts — actual 20 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Obi Toppin</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (11 pts vs 9.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (22 pts vs 20.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 14.5 line, +4.5). Projection model targeted 12.0 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Kobe Brown</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10.5</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 10.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Trend, FG Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -14406,665 +14618,1535 @@
       <c r="D11" t="n">
         <v>8.5</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 9.5 line, +2.5). Projection model called 12.6 pts — actual 12 was 0.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 15.5 line, -4.5). Projection model targeted 18.2 pts (correct direction) but actual was 11. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Kam Jones</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 7.5 line, -0.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 15.5 line, +7.5). Projection model targeted 7.4 pts (correct direction) but actual was 23. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 11.5 line, -0.5). Projection model called 10.6 pts — actual 11 was 0.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 13.5 line, -1.5). Projection model called 13.8 pts — actual 12 was 1.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (21 pts vs 26.5 line, -5.5). Projection model targeted 38.5 pts (correct direction) but actual was 21. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>28.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (19 pts vs 28.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (7 pts vs 5.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (21 pts vs 9.5 line, +11.5).</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (5 pts vs 11.5 line, -6.5). Projection model targeted 19.0 pts (correct direction) but actual was 5. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, Defense.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 15.5 line, +3.5). Projection model targeted 10.8 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (10 pts vs 8.5 line, +1.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Anthony Edwards</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (8 pts vs 24.5 line, -16.5). Underperformed by 16.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: HR L10, Trend, Pace.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (21 pts vs 20.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L10, Defense, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (8 pts vs 13.5 line, -5.5). Projection model targeted 24.8 pts (correct direction) but actual was 8. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 14.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 17.5 line, +7.5). Projection model targeted 15.4 pts (correct direction) but actual was 25. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 11.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (21 pts vs 19.5 line, +1.5). Projection model called 20.5 pts — actual 21 was 0.5 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 10.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (18 pts vs 22.5 line, -4.5). Projection model called 19.4 pts — actual 18 was 1.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 12.5 line, -0.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 8.5 line, -2.5). Projection model called 7.8 pts — actual 6 was 1.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Ziaire Williams</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (8 pts vs 10.5 line, -2.5). Projection model (10.7 pts) and actual (8) both missed the mark. Key signals that disagreed: H2H, Min Trend. Counter-signals that proved correct: H2H, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 11.5 line, -0.5). Projection model called 8.8 pts — actual 11 was 2.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (2 pts vs 7.5 line, -5.5). Projection model targeted 10.6 pts (correct direction) but actual was 2. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 17.5 line, -6.5).</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Mitchell Robinson</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 6.5 line, +10.5). Overperformed by 10.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (7 pts vs 8.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L10, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 12.5 line, -5.5). Projection model called 5.7 pts — actual 7 was 1.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 13.5 line, -0.5). Projection model called 11.8 pts — actual 13 was 1.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>17.5</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (31 pts vs 17.5 line, +13.5). Overperformed by 13.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -15086,25 +16168,63 @@
       <c r="D45" t="n">
         <v>20.5</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>14.5</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 14.5 line, -2.5). Projection model called 12.1 pts — actual 12 was 0.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -15126,45 +16246,109 @@
       <c r="D47" t="n">
         <v>8.5</v>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Josh Giddey</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 15.5 line, -9.5). Underperformed by 9.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>26.5</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (17 pts vs 26.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -15186,65 +16370,155 @@
       <c r="D50" t="n">
         <v>18.5</v>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 12.5 line, -3.5). Projection model called 11.3 pts — actual 9 was 2.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 8.5 line, +4.5). Projection model targeted 5.4 pts (correct direction) but actual was 13. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>16.5</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (16 pts vs 16.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, HR L10, H2H.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -15266,1045 +16540,2409 @@
       <c r="D54" t="n">
         <v>10.5</v>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Myles Turner</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 10.5 line, -6.5). Projection model called 5.4 pts — actual 4 was 1.4 off. Model accuracy strong on this play. Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (26 pts vs 25.5 line, +0.5). Projection model called 27.7 pts — actual 26 was 1.7 off. Model accuracy strong on this play. Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 9.5 line, +9.5). Overperformed by 9.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Kyle Kuzma</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (14 pts vs 12.5 line, +1.5).</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (23 pts vs 22.5 line, +0.5). Projection model called 22.7 pts — actual 23 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E60" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 15.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E61" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (21 pts vs 18.5 line, +2.5). Projection model targeted 16.2 pts (correct direction) but actual was 21. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 15.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L10, Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (27 pts vs 14.5 line, +12.5). Overperformed by 12.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L10, Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (22 pts vs 18.5 line, +3.5). Projection model targeted 14.5 pts (correct direction) but actual was 22. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: FG Trend.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 15.5 line, +2.5). Projection model called 15.9 pts — actual 18 was 2.1 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E66" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (19 pts vs 19.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E67" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (16 pts vs 10.5 line, +5.5).</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 15.5 line, -3.5). Projection model called 14.9 pts — actual 12 was 2.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 23.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (20 pts vs 20.5 line, -0.5). Projection model called 19.3 pts — actual 20 was 0.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (17 pts vs 21.5 line, -4.5). Projection model called 19.3 pts — actual 17 was 2.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (30 pts vs 15.5 line, +14.5).</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Taylor Hendricks</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 9.5 line, -0.5). Projection model called 6.9 pts — actual 9 was 2.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 10.5 line, -3.5). Projection model called 6.5 pts — actual 7 was 0.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 21.5 line, +3.5). Projection model called 24.0 pts — actual 25 was 1.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (11 pts vs 7.5 line, +3.5). Projection model called 8.6 pts — actual 11 was 2.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 18.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 14.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L10, Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 11.5 line, -1.5). Projection model called 9.4 pts — actual 10 was 0.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 11.5 line, -3.5). Projection model called 9.3 pts — actual 8 was 1.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Brandon Williams</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 13.5 line, +9.5). Overperformed by 9.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, Defense.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (28 pts vs 11.5 line, +16.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Daniel Gafford</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E83" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (7 pts vs 11.5 line, -4.5). Projection model targeted 15.1 pts (correct direction) but actual was 7. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, Defense.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (27 pts vs 20.5 line, +6.5).</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 9.5 line, +8.5).</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E86" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 15.5 line, +2.5). Projection model targeted 12.4 pts (correct direction) but actual was 18. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E87" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 16.5 line, -7.5). Projection model called 6.1 pts — actual 9 was 2.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E88" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 14.5 line, +4.5). Projection model targeted 10.5 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Khris Middleton</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (0 pts vs 9.5 line, -9.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (51 pts vs 23.5 line, +27.5). Overperformed by 27.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L10, Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (14 pts vs 9.5 line, +4.5). Projection model targeted 7.0 pts (correct direction) but actual was 14. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, Context.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (19 pts vs 8.5 line, +10.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>23.5</v>
       </c>
+      <c r="E93" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 23.5 line, -13.5).</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Jeremiah Fears</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (28 pts vs 14.5 line, +13.5). Overperformed by 13.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>DeMar DeRozan</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 20.5 line, -6.5). Projection model called 16.7 pts — actual 14 was 2.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E96" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 12.5 line, +10.5). Overperformed by 10.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (13 pts vs 21.5 line, -8.5). Underperformed by 8.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 11.5 line, -3.5). Projection model called 7.6 pts — actual 8 was 0.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E99" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (20 pts vs 19.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E100" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (9 pts vs 13.5 line, -4.5). Projection model (13.8 pts) and actual (9) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Yves Missi</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 6.5 line, -0.5). Projection model called 4.0 pts — actual 6 was 2.0 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E102" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (12 pts vs 15.5 line, -3.5). Projection model targeted 18.6 pts (correct direction) but actual was 12. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E103" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (3 pts vs 9.5 line, -6.5).</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (28 pts vs 14.5 line, +13.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E105" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 21.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Dylan Cardwell</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="4" t="n">
         <v>4.5</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (6 pts vs 4.5 line, +1.5). Projection model called 5.0 pts — actual 6 was 1.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 08:14</t>
+        </is>
       </c>
     </row>
   </sheetData>
